--- a/consulting_forms/011_initial_consultation_questionnaire--consulting_forms.xlsx
+++ b/consulting_forms/011_initial_consultation_questionnaire--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'successful_onboarding'}</t>
+          <t>successful_onboarding</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Successful Onboarding'}</t>
+          <t>Successful Onboarding</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'reschedule_meeting'}</t>
+          <t>reschedule_meeting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Reschedule Meeting'}</t>
+          <t>Reschedule Meeting</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
